--- a/artfynd/A 27915-2026 artfynd.xlsx
+++ b/artfynd/A 27915-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ24"/>
+  <dimension ref="A1:AZ41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -800,46 +800,38 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>135014145</v>
+        <v>136348778</v>
       </c>
       <c r="B3" t="n">
-        <v>57977</v>
+        <v>97551</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>53</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -847,13 +839,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>512698</v>
+        <v>512622</v>
       </c>
       <c r="R3" t="n">
-        <v>6512271</v>
+        <v>6512296</v>
       </c>
       <c r="S3" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -877,22 +869,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>15:42</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>15:42</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -901,69 +883,61 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Daniel Hjelm</t>
+          <t>Emil Lindgren</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Daniel Hjelm</t>
+          <t>Emil Lindgren</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135014145</t>
+          <t>https://artportalen.se/Sighting/136348778</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>135014339</v>
+        <v>136348820</v>
       </c>
       <c r="B4" t="n">
-        <v>57167</v>
+        <v>93378</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100138</v>
+        <v>4364</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -971,13 +945,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>512743</v>
+        <v>512662</v>
       </c>
       <c r="R4" t="n">
-        <v>6512294</v>
+        <v>6512129</v>
       </c>
       <c r="S4" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1001,22 +975,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>15:49</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>15:50</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1025,33 +989,34 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Daniel Hjelm</t>
+          <t>Emil Lindgren</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Daniel Hjelm</t>
+          <t>Emil Lindgren</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135014339</t>
+          <t>https://artportalen.se/Sighting/136348820</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>135014414</v>
+        <v>135014145</v>
       </c>
       <c r="B5" t="n">
-        <v>57167</v>
+        <v>57977</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1059,21 +1024,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1085,7 +1050,7 @@
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -1095,13 +1060,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>512754</v>
+        <v>512698</v>
       </c>
       <c r="R5" t="n">
-        <v>6512293</v>
+        <v>6512271</v>
       </c>
       <c r="S5" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1130,7 +1095,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1140,7 +1105,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1166,16 +1131,16 @@
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135014414</t>
+          <t>https://artportalen.se/Sighting/135014145</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>135009963</v>
+        <v>136348819</v>
       </c>
       <c r="B6" t="n">
-        <v>4776</v>
+        <v>57985</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1183,50 +1148,45 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100299</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Fagerfallet, Ög</t>
+          <t>Bläcksvikebäcken, Ög</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>512777</v>
+        <v>512659</v>
       </c>
       <c r="R6" t="n">
-        <v>6512234</v>
+        <v>6512127</v>
       </c>
       <c r="S6" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1250,22 +1210,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>13:47</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>13:48</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1280,49 +1230,49 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Daniel Hjelm</t>
+          <t>Emil Lindgren</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Daniel Hjelm</t>
+          <t>Emil Lindgren</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135009963</t>
+          <t>https://artportalen.se/Sighting/136348819</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>135012840</v>
+        <v>136342863</v>
       </c>
       <c r="B7" t="n">
-        <v>4776</v>
+        <v>57848</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100299</v>
+        <v>100136</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Lappuggla</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Strix nebulosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>J.R. Forster, 1772</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1330,14 +1280,13 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1345,13 +1294,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>512573</v>
+        <v>512761</v>
       </c>
       <c r="R7" t="n">
-        <v>6512298</v>
+        <v>6512295</v>
       </c>
       <c r="S7" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1375,22 +1324,22 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1416,16 +1365,16 @@
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135012840</t>
+          <t>https://artportalen.se/Sighting/136342863</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>135014006</v>
+        <v>135014339</v>
       </c>
       <c r="B8" t="n">
-        <v>5181</v>
+        <v>57167</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1433,21 +1382,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100526</v>
+        <v>100138</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1455,12 +1404,11 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
@@ -1470,13 +1418,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>512684</v>
+        <v>512743</v>
       </c>
       <c r="R8" t="n">
-        <v>6512277</v>
+        <v>6512294</v>
       </c>
       <c r="S8" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1505,7 +1453,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1515,7 +1463,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1541,38 +1489,38 @@
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135014006</t>
+          <t>https://artportalen.se/Sighting/135014339</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>135011039</v>
+        <v>135014414</v>
       </c>
       <c r="B9" t="n">
-        <v>58141</v>
+        <v>57167</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103021</v>
+        <v>100138</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1584,23 +1532,23 @@
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Fagerfallet, Ög</t>
+          <t>Bläcksvikebäcken, Ög</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>512788</v>
+        <v>512754</v>
       </c>
       <c r="R9" t="n">
-        <v>6512223</v>
+        <v>6512293</v>
       </c>
       <c r="S9" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1629,7 +1577,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1639,7 +1587,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1665,38 +1613,38 @@
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135011039</t>
+          <t>https://artportalen.se/Sighting/135014414</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>135012841</v>
+        <v>136342762</v>
       </c>
       <c r="B10" t="n">
-        <v>58141</v>
+        <v>57175</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103021</v>
+        <v>100138</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1708,7 +1656,7 @@
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
@@ -1718,13 +1666,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>512573</v>
+        <v>512672</v>
       </c>
       <c r="R10" t="n">
-        <v>6512298</v>
+        <v>6512267</v>
       </c>
       <c r="S10" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1748,22 +1696,27 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>16:09</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Fjäder hona</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1789,16 +1742,16 @@
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135012841</t>
+          <t>https://artportalen.se/Sighting/136342762</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>135011037</v>
+        <v>135009963</v>
       </c>
       <c r="B11" t="n">
-        <v>58136</v>
+        <v>4776</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1806,21 +1759,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103023</v>
+        <v>100299</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tofsmes</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lophophanes cristatus</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1828,11 +1781,12 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N11" t="inlineStr"/>
@@ -1842,10 +1796,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>512788</v>
+        <v>512777</v>
       </c>
       <c r="R11" t="n">
-        <v>6512223</v>
+        <v>6512234</v>
       </c>
       <c r="S11" t="n">
         <v>6</v>
@@ -1877,7 +1831,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1887,7 +1841,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1913,38 +1867,38 @@
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135011037</t>
+          <t>https://artportalen.se/Sighting/135009963</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>135011055</v>
+        <v>135012840</v>
       </c>
       <c r="B12" t="n">
-        <v>58629</v>
+        <v>4776</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103042</v>
+        <v>100299</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Grönfink</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Chloris chloris</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1952,24 +1906,25 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Fagerfallet, Ög</t>
+          <t>Bläcksvikebäcken, Ög</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>512788</v>
+        <v>512573</v>
       </c>
       <c r="R12" t="n">
-        <v>6512223</v>
+        <v>6512298</v>
       </c>
       <c r="S12" t="n">
         <v>6</v>
@@ -2001,7 +1956,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2011,7 +1966,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2037,16 +1992,16 @@
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135011055</t>
+          <t>https://artportalen.se/Sighting/135012840</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>135010092</v>
+        <v>136341817</v>
       </c>
       <c r="B13" t="n">
-        <v>5201</v>
+        <v>4777</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2054,21 +2009,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>105930</v>
+        <v>100299</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -2087,17 +2042,17 @@
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Fagerfallet, Ög</t>
+          <t>Tasbygget, Ög</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>512780</v>
+        <v>512701</v>
       </c>
       <c r="R13" t="n">
-        <v>6512217</v>
+        <v>6512060</v>
       </c>
       <c r="S13" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2121,22 +2076,22 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2162,16 +2117,16 @@
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135010092</t>
+          <t>https://artportalen.se/Sighting/136341817</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>135010559</v>
+        <v>135014006</v>
       </c>
       <c r="B14" t="n">
-        <v>8450</v>
+        <v>5181</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2179,21 +2134,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>106554</v>
+        <v>100526</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -2206,23 +2161,23 @@
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Fagerfallet, Ög</t>
+          <t>Bläcksvikebäcken, Ög</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>512804</v>
+        <v>512684</v>
       </c>
       <c r="R14" t="n">
-        <v>6512212</v>
+        <v>6512277</v>
       </c>
       <c r="S14" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2251,7 +2206,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2261,7 +2216,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2287,16 +2242,16 @@
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135010559</t>
+          <t>https://artportalen.se/Sighting/135014006</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>135011600</v>
+        <v>136341818</v>
       </c>
       <c r="B15" t="n">
-        <v>99186</v>
+        <v>5182</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2304,45 +2259,50 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>219790</v>
+        <v>100526</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Bläcksvikebäcken, Ög</t>
+          <t>Tasbygget, Ög</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>512708</v>
+        <v>512701</v>
       </c>
       <c r="R15" t="n">
-        <v>6512239</v>
+        <v>6512060</v>
       </c>
       <c r="S15" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2366,22 +2326,22 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2407,16 +2367,16 @@
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135011600</t>
+          <t>https://artportalen.se/Sighting/136341818</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>135011959</v>
+        <v>136348780</v>
       </c>
       <c r="B16" t="n">
-        <v>99186</v>
+        <v>5182</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2424,31 +2384,28 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>219790</v>
+        <v>100526</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2456,13 +2413,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>512640</v>
+        <v>512693</v>
       </c>
       <c r="R16" t="n">
-        <v>6512269</v>
+        <v>6512254</v>
       </c>
       <c r="S16" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2486,22 +2443,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>14:52</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>14:57</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2510,72 +2457,81 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Daniel Hjelm</t>
+          <t>Emil Lindgren</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Daniel Hjelm</t>
+          <t>Emil Lindgren</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135011959</t>
+          <t>https://artportalen.se/Sighting/136348780</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>135012843</v>
+        <v>135011039</v>
       </c>
       <c r="B17" t="n">
-        <v>99186</v>
+        <v>58141</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>219790</v>
+        <v>103021</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Bläcksvikebäcken, Ög</t>
+          <t>Fagerfallet, Ög</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>512573</v>
+        <v>512788</v>
       </c>
       <c r="R17" t="n">
-        <v>6512298</v>
+        <v>6512223</v>
       </c>
       <c r="S17" t="n">
         <v>6</v>
@@ -2607,7 +2563,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2617,7 +2573,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2643,48 +2599,52 @@
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135012843</t>
+          <t>https://artportalen.se/Sighting/135011039</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>135013927</v>
+        <v>135012841</v>
       </c>
       <c r="B18" t="n">
-        <v>99186</v>
+        <v>58141</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>219790</v>
+        <v>103021</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2692,13 +2652,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>512692</v>
+        <v>512573</v>
       </c>
       <c r="R18" t="n">
-        <v>6512306</v>
+        <v>6512298</v>
       </c>
       <c r="S18" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2727,7 +2687,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2737,7 +2697,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2763,44 +2723,52 @@
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135013927</t>
+          <t>https://artportalen.se/Sighting/135012841</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>135014325</v>
+        <v>136342763</v>
       </c>
       <c r="B19" t="n">
-        <v>99186</v>
+        <v>58149</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>219790</v>
+        <v>103021</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2808,13 +2776,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>512725</v>
+        <v>512672</v>
       </c>
       <c r="R19" t="n">
-        <v>6512290</v>
+        <v>6512267</v>
       </c>
       <c r="S19" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2838,22 +2806,22 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2879,16 +2847,16 @@
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135014325</t>
+          <t>https://artportalen.se/Sighting/136342763</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>135009278</v>
+        <v>135011037</v>
       </c>
       <c r="B20" t="n">
-        <v>106406</v>
+        <v>58136</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2896,35 +2864,35 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>221144</v>
+        <v>103023</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Tofsmes</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Lophophanes cristatus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2932,13 +2900,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>512802</v>
+        <v>512788</v>
       </c>
       <c r="R20" t="n">
-        <v>6512272</v>
+        <v>6512223</v>
       </c>
       <c r="S20" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2967,7 +2935,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2977,7 +2945,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3003,44 +2971,52 @@
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135009278</t>
+          <t>https://artportalen.se/Sighting/135011037</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>135010561</v>
+        <v>135011055</v>
       </c>
       <c r="B21" t="n">
-        <v>98131</v>
+        <v>58629</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>221945</v>
+        <v>103042</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Grönfink</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Chloris chloris</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -3048,13 +3024,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>512804</v>
+        <v>512788</v>
       </c>
       <c r="R21" t="n">
-        <v>6512212</v>
+        <v>6512223</v>
       </c>
       <c r="S21" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3083,7 +3059,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3093,7 +3069,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3119,16 +3095,16 @@
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135010561</t>
+          <t>https://artportalen.se/Sighting/135011055</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>135011599</v>
+        <v>135010092</v>
       </c>
       <c r="B22" t="n">
-        <v>98131</v>
+        <v>5201</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3136,41 +3112,50 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>221945</v>
+        <v>105930</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Bläcksvikebäcken, Ög</t>
+          <t>Fagerfallet, Ög</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>512708</v>
+        <v>512780</v>
       </c>
       <c r="R22" t="n">
-        <v>6512239</v>
+        <v>6512217</v>
       </c>
       <c r="S22" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3199,7 +3184,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3209,7 +3194,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3235,16 +3220,16 @@
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135011599</t>
+          <t>https://artportalen.se/Sighting/135010092</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>135011971</v>
+        <v>136341631</v>
       </c>
       <c r="B23" t="n">
-        <v>98131</v>
+        <v>5202</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3252,41 +3237,50 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>221945</v>
+        <v>105930</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Bläcksvikebäcken, Ög</t>
+          <t>Tasbygget, Ög</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>512633</v>
+        <v>512686</v>
       </c>
       <c r="R23" t="n">
-        <v>6512286</v>
+        <v>6512054</v>
       </c>
       <c r="S23" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3310,22 +3304,22 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3351,16 +3345,16 @@
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135011971</t>
+          <t>https://artportalen.se/Sighting/136341631</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>135013926</v>
+        <v>135010559</v>
       </c>
       <c r="B24" t="n">
-        <v>98131</v>
+        <v>8450</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3368,41 +3362,50 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>221945</v>
+        <v>106554</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Bläcksvikebäcken, Ög</t>
+          <t>Fagerfallet, Ög</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>512692</v>
+        <v>512804</v>
       </c>
       <c r="R24" t="n">
-        <v>6512306</v>
+        <v>6512212</v>
       </c>
       <c r="S24" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3431,7 +3434,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3441,7 +3444,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3467,7 +3470,2004 @@
       <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
         <is>
+          <t>https://artportalen.se/Sighting/135010559</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>136342764</v>
+      </c>
+      <c r="B25" t="n">
+        <v>58850</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>208250</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Åkergroda</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Rana arvalis</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Nilsson, 1842</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Bläcksvikebäcken, Ög</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>512672</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6512267</v>
+      </c>
+      <c r="S25" t="n">
+        <v>9</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Motala</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Godegård</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>16:09</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>16:09</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Daniel Hjelm</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Daniel Hjelm</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136342764</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>135011600</v>
+      </c>
+      <c r="B26" t="n">
+        <v>99186</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Bläcksvikebäcken, Ög</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>512708</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6512239</v>
+      </c>
+      <c r="S26" t="n">
+        <v>8</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Motala</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Godegård</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>14:39</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>14:47</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Daniel Hjelm</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Daniel Hjelm</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135011600</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>135011959</v>
+      </c>
+      <c r="B27" t="n">
+        <v>99186</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Bläcksvikebäcken, Ög</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>512640</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6512269</v>
+      </c>
+      <c r="S27" t="n">
+        <v>5</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Motala</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Godegård</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>14:52</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>14:57</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Daniel Hjelm</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Daniel Hjelm</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135011959</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>135012843</v>
+      </c>
+      <c r="B28" t="n">
+        <v>99186</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Bläcksvikebäcken, Ög</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>512573</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6512298</v>
+      </c>
+      <c r="S28" t="n">
+        <v>6</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Motala</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Godegård</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>15:15</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>15:15</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Daniel Hjelm</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Daniel Hjelm</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135012843</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>135013927</v>
+      </c>
+      <c r="B29" t="n">
+        <v>99186</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Bläcksvikebäcken, Ög</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>512692</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6512306</v>
+      </c>
+      <c r="S29" t="n">
+        <v>5</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Motala</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Godegård</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>15:33</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>15:35</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Daniel Hjelm</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Daniel Hjelm</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135013927</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>135014325</v>
+      </c>
+      <c r="B30" t="n">
+        <v>99186</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Bläcksvikebäcken, Ög</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>512725</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6512290</v>
+      </c>
+      <c r="S30" t="n">
+        <v>7</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Motala</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Godegård</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>15:48</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>15:48</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Daniel Hjelm</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Daniel Hjelm</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135014325</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>136339655</v>
+      </c>
+      <c r="B31" t="n">
+        <v>99231</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Fagerfallet, Ög</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>512801</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6512188</v>
+      </c>
+      <c r="S31" t="n">
+        <v>12</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Motala</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Godegård</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>13:40</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>13:41</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Daniel Hjelm</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Daniel Hjelm</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136339655</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>136341916</v>
+      </c>
+      <c r="B32" t="n">
+        <v>99231</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Lillsjölund, Ög</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>512703</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6512174</v>
+      </c>
+      <c r="S32" t="n">
+        <v>11</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Motala</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Godegård</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>15:36</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>15:37</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Daniel Hjelm</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Daniel Hjelm</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136341916</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>136342257</v>
+      </c>
+      <c r="B33" t="n">
+        <v>99231</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Lillsjölund, Ög</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>512564</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6512216</v>
+      </c>
+      <c r="S33" t="n">
+        <v>7</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Motala</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Godegård</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>15:46</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>15:46</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Daniel Hjelm</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Daniel Hjelm</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136342257</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>136342456</v>
+      </c>
+      <c r="B34" t="n">
+        <v>99231</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Lillsjölund, Ög</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>512561</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6512241</v>
+      </c>
+      <c r="S34" t="n">
+        <v>11</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Motala</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Godegård</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>15:50</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>15:50</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Daniel Hjelm</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Daniel Hjelm</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136342456</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>135009278</v>
+      </c>
+      <c r="B35" t="n">
+        <v>106406</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Fagerfallet, Ög</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>512802</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6512272</v>
+      </c>
+      <c r="S35" t="n">
+        <v>5</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Motala</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Godegård</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>13:26</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>13:27</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Daniel Hjelm</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Daniel Hjelm</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135009278</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>136342923</v>
+      </c>
+      <c r="B36" t="n">
+        <v>106455</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Bläcksvikebäcken, Ög</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>512763</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6512290</v>
+      </c>
+      <c r="S36" t="n">
+        <v>14</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Motala</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Godegård</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Daniel Hjelm</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Daniel Hjelm</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136342923</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>135010561</v>
+      </c>
+      <c r="B37" t="n">
+        <v>98131</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Fagerfallet, Ög</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>512804</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6512212</v>
+      </c>
+      <c r="S37" t="n">
+        <v>3</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Motala</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Godegård</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>14:11</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>14:11</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Daniel Hjelm</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Daniel Hjelm</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135010561</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>135011599</v>
+      </c>
+      <c r="B38" t="n">
+        <v>98131</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Bläcksvikebäcken, Ög</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>512708</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6512239</v>
+      </c>
+      <c r="S38" t="n">
+        <v>8</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Motala</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Godegård</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>14:39</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>14:47</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Daniel Hjelm</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Daniel Hjelm</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135011599</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>135011971</v>
+      </c>
+      <c r="B39" t="n">
+        <v>98131</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Bläcksvikebäcken, Ög</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>512633</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6512286</v>
+      </c>
+      <c r="S39" t="n">
+        <v>6</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Motala</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Godegård</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>14:58</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>14:58</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Daniel Hjelm</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Daniel Hjelm</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135011971</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>135013926</v>
+      </c>
+      <c r="B40" t="n">
+        <v>98131</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Bläcksvikebäcken, Ög</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>512692</v>
+      </c>
+      <c r="R40" t="n">
+        <v>6512306</v>
+      </c>
+      <c r="S40" t="n">
+        <v>5</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Motala</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Godegård</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>15:33</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>15:35</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Daniel Hjelm</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Daniel Hjelm</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
           <t>https://artportalen.se/Sighting/135013926</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>136338975</v>
+      </c>
+      <c r="B41" t="n">
+        <v>98176</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Bläcksvikebäcken, Ög</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>512754</v>
+      </c>
+      <c r="R41" t="n">
+        <v>6512297</v>
+      </c>
+      <c r="S41" t="n">
+        <v>11</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Motala</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Godegård</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>13:16</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>13:17</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Daniel Hjelm</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Daniel Hjelm</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136338975</t>
         </is>
       </c>
     </row>
@@ -3496,6 +5496,23 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 27915-2026 artfynd.xlsx
+++ b/artfynd/A 27915-2026 artfynd.xlsx
@@ -803,7 +803,7 @@
         <v>136348778</v>
       </c>
       <c r="B3" t="n">
-        <v>97551</v>
+        <v>97564</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -910,7 +910,7 @@
         <v>136348820</v>
       </c>
       <c r="B4" t="n">
-        <v>93378</v>
+        <v>93385</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1140,7 +1140,7 @@
         <v>136348819</v>
       </c>
       <c r="B6" t="n">
-        <v>57985</v>
+        <v>57990</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1250,7 +1250,7 @@
         <v>136342863</v>
       </c>
       <c r="B7" t="n">
-        <v>57848</v>
+        <v>57853</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1622,7 +1622,7 @@
         <v>136342762</v>
       </c>
       <c r="B10" t="n">
-        <v>57175</v>
+        <v>57180</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -2732,7 +2732,7 @@
         <v>136342763</v>
       </c>
       <c r="B19" t="n">
-        <v>58149</v>
+        <v>58154</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -3479,7 +3479,7 @@
         <v>136342764</v>
       </c>
       <c r="B25" t="n">
-        <v>58850</v>
+        <v>58855</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -4192,7 +4192,7 @@
         <v>136339655</v>
       </c>
       <c r="B31" t="n">
-        <v>99231</v>
+        <v>99244</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4308,7 +4308,7 @@
         <v>136341916</v>
       </c>
       <c r="B32" t="n">
-        <v>99231</v>
+        <v>99244</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4424,7 +4424,7 @@
         <v>136342257</v>
       </c>
       <c r="B33" t="n">
-        <v>99231</v>
+        <v>99244</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4540,7 +4540,7 @@
         <v>136342456</v>
       </c>
       <c r="B34" t="n">
-        <v>99231</v>
+        <v>99244</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4780,7 +4780,7 @@
         <v>136342923</v>
       </c>
       <c r="B36" t="n">
-        <v>106455</v>
+        <v>106468</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -5360,7 +5360,7 @@
         <v>136338975</v>
       </c>
       <c r="B41" t="n">
-        <v>98176</v>
+        <v>98189</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>

--- a/artfynd/A 27915-2026 artfynd.xlsx
+++ b/artfynd/A 27915-2026 artfynd.xlsx
@@ -803,7 +803,7 @@
         <v>136348778</v>
       </c>
       <c r="B3" t="n">
-        <v>97564</v>
+        <v>97565</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -910,7 +910,7 @@
         <v>136348820</v>
       </c>
       <c r="B4" t="n">
-        <v>93385</v>
+        <v>93386</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -4192,7 +4192,7 @@
         <v>136339655</v>
       </c>
       <c r="B31" t="n">
-        <v>99244</v>
+        <v>99245</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4308,7 +4308,7 @@
         <v>136341916</v>
       </c>
       <c r="B32" t="n">
-        <v>99244</v>
+        <v>99245</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4424,7 +4424,7 @@
         <v>136342257</v>
       </c>
       <c r="B33" t="n">
-        <v>99244</v>
+        <v>99245</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4540,7 +4540,7 @@
         <v>136342456</v>
       </c>
       <c r="B34" t="n">
-        <v>99244</v>
+        <v>99245</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4780,7 +4780,7 @@
         <v>136342923</v>
       </c>
       <c r="B36" t="n">
-        <v>106468</v>
+        <v>106469</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -5360,7 +5360,7 @@
         <v>136338975</v>
       </c>
       <c r="B41" t="n">
-        <v>98189</v>
+        <v>98190</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>

--- a/artfynd/A 27915-2026 artfynd.xlsx
+++ b/artfynd/A 27915-2026 artfynd.xlsx
@@ -803,7 +803,7 @@
         <v>136348778</v>
       </c>
       <c r="B3" t="n">
-        <v>97565</v>
+        <v>97578</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -910,7 +910,7 @@
         <v>136348820</v>
       </c>
       <c r="B4" t="n">
-        <v>93386</v>
+        <v>93399</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1140,7 +1140,7 @@
         <v>136348819</v>
       </c>
       <c r="B6" t="n">
-        <v>57990</v>
+        <v>58003</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1250,7 +1250,7 @@
         <v>136342863</v>
       </c>
       <c r="B7" t="n">
-        <v>57853</v>
+        <v>57866</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1622,7 +1622,7 @@
         <v>136342762</v>
       </c>
       <c r="B10" t="n">
-        <v>57180</v>
+        <v>57193</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -2732,7 +2732,7 @@
         <v>136342763</v>
       </c>
       <c r="B19" t="n">
-        <v>58154</v>
+        <v>58167</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -3479,7 +3479,7 @@
         <v>136342764</v>
       </c>
       <c r="B25" t="n">
-        <v>58855</v>
+        <v>58868</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -4192,7 +4192,7 @@
         <v>136339655</v>
       </c>
       <c r="B31" t="n">
-        <v>99245</v>
+        <v>99258</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4308,7 +4308,7 @@
         <v>136341916</v>
       </c>
       <c r="B32" t="n">
-        <v>99245</v>
+        <v>99258</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4424,7 +4424,7 @@
         <v>136342257</v>
       </c>
       <c r="B33" t="n">
-        <v>99245</v>
+        <v>99258</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4540,7 +4540,7 @@
         <v>136342456</v>
       </c>
       <c r="B34" t="n">
-        <v>99245</v>
+        <v>99258</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4780,7 +4780,7 @@
         <v>136342923</v>
       </c>
       <c r="B36" t="n">
-        <v>106469</v>
+        <v>106482</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -5360,7 +5360,7 @@
         <v>136338975</v>
       </c>
       <c r="B41" t="n">
-        <v>98190</v>
+        <v>98203</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>

--- a/artfynd/A 27915-2026 artfynd.xlsx
+++ b/artfynd/A 27915-2026 artfynd.xlsx
@@ -803,7 +803,7 @@
         <v>136348778</v>
       </c>
       <c r="B3" t="n">
-        <v>97578</v>
+        <v>97579</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -910,7 +910,7 @@
         <v>136348820</v>
       </c>
       <c r="B4" t="n">
-        <v>93399</v>
+        <v>93400</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -4192,7 +4192,7 @@
         <v>136339655</v>
       </c>
       <c r="B31" t="n">
-        <v>99258</v>
+        <v>99259</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4308,7 +4308,7 @@
         <v>136341916</v>
       </c>
       <c r="B32" t="n">
-        <v>99258</v>
+        <v>99259</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4424,7 +4424,7 @@
         <v>136342257</v>
       </c>
       <c r="B33" t="n">
-        <v>99258</v>
+        <v>99259</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4540,7 +4540,7 @@
         <v>136342456</v>
       </c>
       <c r="B34" t="n">
-        <v>99258</v>
+        <v>99259</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4780,7 +4780,7 @@
         <v>136342923</v>
       </c>
       <c r="B36" t="n">
-        <v>106482</v>
+        <v>106483</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -5360,7 +5360,7 @@
         <v>136338975</v>
       </c>
       <c r="B41" t="n">
-        <v>98203</v>
+        <v>98204</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
